--- a/data/50001591 - ZITRON COLOMBIA ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA ARIS MARAMTO.xlsx
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46239.60969225694</v>
+        <v>46239.716654814816</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>156</v>
